--- a/astro-site/public/dl/wedding-venue-business-plan/wedding-venue-financial-projections.xlsx
+++ b/astro-site/public/dl/wedding-venue-business-plan/wedding-venue-financial-projections.xlsx
@@ -825,7 +825,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Menu price incl. sales tax (calculated)</t>
+          <t>Revenue per guest incl. sales tax (calculated)</t>
         </is>
       </c>
       <c r="B9" s="80">
@@ -1236,7 +1236,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sales tax rate on sales</t>
+          <t>Sales tax rate on food sales (not used: the venue sells no food)</t>
         </is>
       </c>
       <c r="B39" s="63" t="n">
@@ -1251,7 +1251,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sales tax rate on alcohol to go</t>
+          <t>General sales tax rate (reference only: the rates used are on the P&amp;L)</t>
         </is>
       </c>
       <c r="B40" s="63" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>General example rate, 8%. In this plan it applies to everything the venue bills as rental and services; the caterer commission is taxed at 0% in the model, and the venue's purchases carry no recoverable credit. The venue does not sell food or beverage: the caterer bills the menu and the bar. Some states do not tax venue fees at all: confirm yours with your state department of revenue</t>
+          <t>REFERENCE ONLY: no formula reads this cell. The sales tax the venue collects is typed in the "Sales tax rate on the line (%)" column of the "3-Year P&amp;L": 8% on venue rental &amp; services (G10) and 0% on the caterer commission (G11) in the example. The venue does not sell food or beverage: the caterer bills the menu and the bar. Some states do not tax venue fees at all: confirm yours with your state department of revenue</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="D10" s="28" t="inlineStr">
         <is>
-          <t>Sprinklers need city water; a tank and fire pump, a new septic system or a strict county can double this line. Whether you need them depends on the fire code your county has adopted: ask the building official and the fire marshal in writing, and get local quotes</t>
+          <t>Sprinklers need enough water flow: without city water, a tank and fire pump, a new septic system or a strict county can double this line. Whether you need them depends on the fire code your county has adopted: ask the building official and the fire marshal in writing, and get local quotes</t>
         </is>
       </c>
       <c r="E10" s="31" t="inlineStr">
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="B20" s="78" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="28" t="n"/>
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="B21" s="78" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="28" t="n"/>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B24" s="39">
         <f>IFERROR(IF(OR(B20="",B21="",'0. Assumptions'!$B$6=""),"",B20*B21*'0. Assumptions'!$B$6+B22*B23*'0. Assumptions'!$B$6),"")</f>
-        <v>5716.0</v>
+        <v>5879.5</v>
       </c>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="28" t="n"/>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="B26" s="66">
         <f>IFERROR(B25/B24,"")</f>
-        <v>1.1910426871938418</v>
+        <v>1.1579215919721064</v>
       </c>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D36" s="46" t="inlineStr">
         <is>
-          <t>Weddings 130 guests × ($9,000 site fee + 10% of $110 F&amp;B per guest), corporate 70 × ($3,500 + 10% of $50), private 80 × ($4,000 + 10% of $55), micro 30 × ($2,000 + 10% of $80), excl. sales tax</t>
+          <t>Per event, excl. sales tax: wedding (130 guests) $9,000 site fee + 10% of $110 F&amp;B per guest; corporate (70) $3,500 + 10% of $50; private (80) $4,000 + 10% of $55; micro wedding (30) $2,000 + 10% of $80</t>
         </is>
       </c>
       <c r="E36" s="28" t="n"/>
@@ -7114,17 +7114,17 @@
       </c>
       <c r="B47" s="28" t="inlineStr">
         <is>
-          <t>A well that serves your guests may count as a public water system</t>
+          <t>A public water system if it regularly serves an average of 25 or more people a day at least 60 days a year</t>
         </is>
       </c>
       <c r="C47" s="28" t="inlineStr">
         <is>
-          <t>Ask your state drinking water program</t>
+          <t>40 CFR 141.2 (EPA); your state drinking water program applies it</t>
         </is>
       </c>
       <c r="D47" s="46" t="inlineStr">
         <is>
-          <t>Testing and a permit before the first event</t>
+          <t>Ask your state program about testing and a permit before the first event</t>
         </is>
       </c>
       <c r="E47" s="28" t="n"/>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
-          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10: December, March and June with Month 1 in September; the fourth quarter is remitted in Month 13): if your state requires monthly filing, expect smaller payments every month instead</t>
+          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10: June, September and December with Month 1 in March; the fourth quarter is remitted in Month 13): if your state requires monthly filing, expect smaller payments every month instead</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/wedding-venue-business-plan/wedding-venue-financial-projections.xlsx
+++ b/astro-site/public/dl/wedding-venue-business-plan/wedding-venue-financial-projections.xlsx
@@ -833,7 +833,7 @@
         <v>72.7872</v>
       </c>
       <c r="C9" t="str">
-        <f>IFERROR("Revenue per guest excl. sales tax plus the weighted sales tax of your two sales lines ("&amp;TEXT(SUMPRODUCT('3-Year P&amp;L'!$E$10:$E$11,'3-Year P&amp;L'!$G$10:$G$11)*100,"0")&amp;"%), rounded. It is what the venue bills per guest (venue rental &amp; services plus the caterer commission), not what the couple pays for the whole wedding: the caterer bills the menu and the bar, with its own sales tax, and they are not in this workbook. In the UK, prices to private clients include VAT.","")</f>
+        <f>IFERROR("Revenue per guest excl. sales tax plus the weighted sales tax of your two sales lines ("&amp;TEXT(SUMPRODUCT('3-Year P&amp;L'!$E$10:$E$11,'3-Year P&amp;L'!$G$10:$G$11)*100,"0")&amp;"%), rounded. It is what the venue bills per guest (venue rental &amp; services plus the caterer commission), not what the couple pays for the whole wedding: the caterer bills the menu and the bar, with its own sales tax, and they are not in "&amp;"this workbook. In the UK, prices to private clients include VAT.","")</f>
         <v>Revenue per guest excl. sales tax plus the weighted sales tax of your two sales lines (7%), rounded. It is what the venue bills per guest (venue rental &amp; services plus the caterer commission), not what the couple pays for the whole wedding: the caterer bills the menu and the bar, with its own sales tax, and they are not in this workbook. In the UK, prices to private clients include VAT.</v>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
         <v>0.05524734010187908</v>
       </c>
       <c r="D28" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (architect, engineer &amp; code consultant; barn renovation; fire sprinkler system; ADA-compliant restrooms; electrical service &amp; lighting; HVAC; caterer's prep &amp; warming kitchen; parking lot &amp; driveway; landscaping; fire alarm, exit signs &amp; accessible routes), not of the whole block: the other items are left out. Sprinklers on a tank and fire pump, a new septic system or a strict county can push these lines far above the example. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (architect, engineer &amp; code consultant; barn renovation; fire sprinkler system; ADA-compliant restrooms; electrical service &amp; lighting; HVAC; caterer's prep &amp; warming kitchen; parking lot &amp; driveway; "&amp;"landscaping; fire alarm, exit signs &amp; accessible routes), not of the whole block: the other items are left out. Sprinklers on a tank and fire pump, a new septic system or a strict county can push these lines far above the example. No "&amp;"lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
         <v>At 10% of the BUILD-OUT items of this block (architect, engineer &amp; code consultant; barn renovation; fire sprinkler system; ADA-compliant restrooms; electrical service &amp; lighting; HVAC; caterer's prep &amp; warming kitchen; parking lot &amp; driveway; landscaping; fire alarm, exit signs &amp; accessible routes), not of the whole block: the other items are left out. Sprinklers on a tank and fire pump, a new septic system or a strict county can push these lines far above the example. No lender funds a build-out without a cushion: the percentage is in "0. Assumptions"</v>
       </c>
       <c r="E28" s="28" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="25" t="str">
-        <f>IFERROR("Not depreciated, because they are not fixed assets: conditional use permit, studies and permit fees; website, photography, video &amp; brand; LLC formation &amp; attorney; launch; lease security deposit; rent during permitting and build-out, and the working capital reserve. They add up to "&amp;TEXT(B31-B36-B37,"#,##0")&amp;" of the "&amp;TEXT(B31,"#,##0")&amp;" total investment.","")</f>
+        <f>IFERROR("Not depreciated, because they are not fixed assets: conditional use permit, studies and permit fees; website, photography, video &amp; brand; LLC formation &amp; attorney; launch; lease security deposit; rent during permitting and build-out, and "&amp;"the working capital reserve. They add up to "&amp;TEXT(B31-B36-B37,"#,##0")&amp;" of the "&amp;TEXT(B31,"#,##0")&amp;" total investment.","")</f>
         <v>Not depreciated, because they are not fixed assets: conditional use permit, studies and permit fees; website, photography, video &amp; brand; LLC formation &amp; attorney; launch; lease security deposit; rent during permitting and build-out, and the working capital reserve. They add up to 165716 of the 669716 total investment.</v>
       </c>
       <c r="E38" s="28" t="n"/>
@@ -2754,7 +2754,7 @@
         <v>0.1056</v>
       </c>
       <c r="F13" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$13,"0%")&amp;" of VENUE RENTAL &amp; SERVICES sales, not of total sales: the caterer commission has its own line · Cleaning and turnover, restroom restocking, generator fuel, parking attendants and security for each event: check it against your invoices and the Pricing &amp; Quote Calculator","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$13,"0%")&amp;" of VENUE RENTAL &amp; SERVICES sales, not of total sales: the caterer commission has its own line · Cleaning and turnover, restroom restocking, generator fuel, parking attendants and security for each event: check it against your invoices and "&amp;"the Pricing &amp; Quote Calculator","")</f>
         <v>At 12% of VENUE RENTAL &amp; SERVICES sales, not of total sales: the caterer commission has its own line · Cleaning and turnover, restroom restocking, generator fuel, parking attendants and security for each event: check it against your invoices and the Pricing &amp; Quote Calculator</v>
       </c>
       <c r="G13" s="75" t="n">

--- a/astro-site/public/dl/wedding-venue-business-plan/wedding-venue-financial-projections.xlsx
+++ b/astro-site/public/dl/wedding-venue-business-plan/wedding-venue-financial-projections.xlsx
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How far you can fall below plan before you start losing money</t>
+          <t>How far planned sales must sit above cash break-even (fixed costs and the loan payment). The drop you can absorb is somewhat smaller: with a 15% cushion, about 13% of plan</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>How far you can fall before you cannot pay the fixed costs and the loan payment. The required minimum is set in the "0. Assumptions" tab</t>
+          <t>How far planned sales sit above cash break-even. The drop you can absorb before you cannot pay the fixed costs and the loan payment is somewhat smaller: with a 25% cushion, 20%. The required minimum is set in the "0. Assumptions" tab</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>

--- a/astro-site/public/dl/wedding-venue-business-plan/wedding-venue-financial-projections.xlsx
+++ b/astro-site/public/dl/wedding-venue-business-plan/wedding-venue-financial-projections.xlsx
@@ -833,7 +833,7 @@
         <v>72.7872</v>
       </c>
       <c r="C9" t="str">
-        <f>IFERROR("Revenue per guest excl. sales tax plus the weighted sales tax of your two sales lines ("&amp;TEXT(SUMPRODUCT('3-Year P&amp;L'!$E$10:$E$11,'3-Year P&amp;L'!$G$10:$G$11)*100,"0")&amp;"%), rounded. It is what the venue bills per guest (venue rental &amp; services plus the caterer commission), not what the couple pays for the whole wedding: the caterer bills the menu and the bar, with its own sales tax, and they are not in this workbook. In the UK, prices to private clients include VAT.","")</f>
+        <f>IFERROR("Revenue per guest excl. sales tax plus the weighted sales tax of your two sales lines ("&amp;TEXT(SUMPRODUCT('3-Year P&amp;L'!$E$10:$E$11,'3-Year P&amp;L'!$G$10:$G$11)*100,"0")&amp;"%), rounded. It is what the venue bills per guest (venue rental &amp; services plus the caterer commission), not what the couple pays for the whole wedding: the caterer bills the menu and the bar, with its own sales tax, and they are not in "&amp;"this workbook. In the UK, prices to private clients include VAT.","")</f>
         <v>Revenue per guest excl. sales tax plus the weighted sales tax of your two sales lines (7%), rounded. It is what the venue bills per guest (venue rental &amp; services plus the caterer commission), not what the couple pays for the whole wedding: the caterer bills the menu and the bar, with its own sales tax, and they are not in this workbook. In the UK, prices to private clients include VAT.</v>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How far you can fall below plan before you start losing money</t>
+          <t>How far planned sales must sit above cash break-even (fixed costs and the loan payment). The drop you can absorb is somewhat smaller: with a 15% cushion, about 13% of plan</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
         <v>0.05524734010187908</v>
       </c>
       <c r="D28" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (architect, engineer &amp; code consultant; barn renovation; fire sprinkler system; ADA-compliant restrooms; electrical service &amp; lighting; HVAC; caterer's prep &amp; warming kitchen; parking lot &amp; driveway; landscaping; fire alarm, exit signs &amp; accessible routes), not of the whole block: the other items are left out. Sprinklers on a tank and fire pump, a new septic system or a strict county can push these lines far above the example. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (architect, engineer &amp; code consultant; barn renovation; fire sprinkler system; ADA-compliant restrooms; electrical service &amp; lighting; HVAC; caterer's prep &amp; warming kitchen; parking lot &amp; driveway; "&amp;"landscaping; fire alarm, exit signs &amp; accessible routes), not of the whole block: the other items are left out. Sprinklers on a tank and fire pump, a new septic system or a strict county can push these lines far above the example. No "&amp;"lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
         <v>At 10% of the BUILD-OUT items of this block (architect, engineer &amp; code consultant; barn renovation; fire sprinkler system; ADA-compliant restrooms; electrical service &amp; lighting; HVAC; caterer's prep &amp; warming kitchen; parking lot &amp; driveway; landscaping; fire alarm, exit signs &amp; accessible routes), not of the whole block: the other items are left out. Sprinklers on a tank and fire pump, a new septic system or a strict county can push these lines far above the example. No lender funds a build-out without a cushion: the percentage is in "0. Assumptions"</v>
       </c>
       <c r="E28" s="28" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="25" t="str">
-        <f>IFERROR("Not depreciated, because they are not fixed assets: conditional use permit, studies and permit fees; website, photography, video &amp; brand; LLC formation &amp; attorney; launch; lease security deposit; rent during permitting and build-out, and the working capital reserve. They add up to "&amp;TEXT(B31-B36-B37,"#,##0")&amp;" of the "&amp;TEXT(B31,"#,##0")&amp;" total investment.","")</f>
+        <f>IFERROR("Not depreciated, because they are not fixed assets: conditional use permit, studies and permit fees; website, photography, video &amp; brand; LLC formation &amp; attorney; launch; lease security deposit; rent during permitting and build-out, and "&amp;"the working capital reserve. They add up to "&amp;TEXT(B31-B36-B37,"#,##0")&amp;" of the "&amp;TEXT(B31,"#,##0")&amp;" total investment.","")</f>
         <v>Not depreciated, because they are not fixed assets: conditional use permit, studies and permit fees; website, photography, video &amp; brand; LLC formation &amp; attorney; launch; lease security deposit; rent during permitting and build-out, and the working capital reserve. They add up to 165716 of the 669716 total investment.</v>
       </c>
       <c r="E38" s="28" t="n"/>
@@ -2754,7 +2754,7 @@
         <v>0.1056</v>
       </c>
       <c r="F13" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$13,"0%")&amp;" of VENUE RENTAL &amp; SERVICES sales, not of total sales: the caterer commission has its own line · Cleaning and turnover, restroom restocking, generator fuel, parking attendants and security for each event: check it against your invoices and the Pricing &amp; Quote Calculator","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$13,"0%")&amp;" of VENUE RENTAL &amp; SERVICES sales, not of total sales: the caterer commission has its own line · Cleaning and turnover, restroom restocking, generator fuel, parking attendants and security for each event: check it against your invoices and "&amp;"the Pricing &amp; Quote Calculator","")</f>
         <v>At 12% of VENUE RENTAL &amp; SERVICES sales, not of total sales: the caterer commission has its own line · Cleaning and turnover, restroom restocking, generator fuel, parking attendants and security for each event: check it against your invoices and the Pricing &amp; Quote Calculator</v>
       </c>
       <c r="G13" s="75" t="n">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>How far you can fall before you cannot pay the fixed costs and the loan payment. The required minimum is set in the "0. Assumptions" tab</t>
+          <t>How far planned sales sit above cash break-even. The drop you can absorb before you cannot pay the fixed costs and the loan payment is somewhat smaller: with a 25% cushion, 20%. The required minimum is set in the "0. Assumptions" tab</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>
